--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AccountAmount.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AccountAmount.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -74,6 +74,10 @@
   </si>
   <si>
     <t>科目发生额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -452,18 +456,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="2" max="3" width="17.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.375" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -471,29 +475,32 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="E7" s="2"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
